--- a/stories/arbres/ATOM-SEC.MAI.003-07.xlsx
+++ b/stories/arbres/ATOM-SEC.MAI.003-07.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Yseult est sur le balcon avec papa. Papa, c'est l'adulte. Yseult reste derrière la protection. Ses pieds restent au sol. Le vent est doux. Yseult tient le manteau de papa. Papa dit : pieds au sol. Derrière la protection. Avec un adulte. Yseult regarde les toits. Elle ne bouge pas les pieds. Papa sourit. Ils rentrent ensemble.</t>
+          <t>Yseult est sur le balcon avec papa. Papa, c'est l'adulte. Yseult reste derrière la protection. Ses pieds restent au sol. Le vent est doux. Yseult tient le manteau de papa. Pieds au sol. Derrière la protection. Avec un adulte. Yseult regarde les toits. Elle ne bouge pas les pieds. Papa sourit. Ils rentrent ensemble.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,13 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Yseult est sur le balcon avec papa. Papa, c'est l'adulte. Yseult reste derrière la protection. Ses pieds restent au sol. Le vent est doux. Yseult tient le manteau de papa.
+papa|Pieds au sol. Derrière la protection. Avec un adulte.
+narrateur|Yseult regarde les toits. Elle ne bouge pas les pieds. Papa sourit. Ils rentrent ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1469,6 +1492,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Yseult est sur le balcon. Que fait-elle ?</t>
         </is>
       </c>
     </row>
@@ -1641,6 +1669,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Yseult a gardé les pieds au sol. Derrière la protection. Avec papa, l'adulte.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1803,6 +1836,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Papa ferme la porte. Yseult s'assoit.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1965,6 +2003,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1983,7 +2026,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2000,6 +2043,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SEC.MAI.003-07.xlsx
+++ b/stories/arbres/ATOM-SEC.MAI.003-07.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1312,6 +1317,7 @@
 narrateur|Yseult regarde les toits. Elle ne bouge pas les pieds. Papa sourit. Ils rentrent ensemble.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1499,6 +1505,7 @@
           <t>narrateur|Yseult est sur le balcon. Que fait-elle ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1674,6 +1681,7 @@
           <t>narrateur|Yseult a gardé les pieds au sol. Derrière la protection. Avec papa, l'adulte.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1841,6 +1849,7 @@
           <t>narrateur|Papa ferme la porte. Yseult s'assoit.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2008,6 +2017,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2026,7 +2036,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2050,6 +2060,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2064,7 +2088,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2251,6 +2275,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-SEC.MAI.003-07.xlsx
+++ b/stories/arbres/ATOM-SEC.MAI.003-07.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Yseult au balcon avec papa</t>
+          <t>Les toits mouillés de Victorina</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Après la pluie, Victorina et papa regardent les toits depuis le balcon. Pieds au sol, derrière la protection, avec papa.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Yseult est sur le balcon avec papa. Papa, c'est l'adulte. Yseult reste derrière la protection. Ses pieds restent au sol. Le vent est doux. Yseult tient le manteau de papa. Pieds au sol. Derrière la protection. Avec un adulte. Yseult regarde les toits. Elle ne bouge pas les pieds. Papa sourit. Ils rentrent ensemble.</t>
+          <t>Une goutte glisse sur une feuille. La feuille est d'un géranium rouge. Les tuiles brillent encore. La cuisine sent la soupe. Un chat gris s'assoit sur le toit d'à côté. Le rideau jaune bouge un peu. Tu as vu le chat, Victorina ? Il est tout gris, papa. Oui. Il se tient tranquille. Le carreau près de la porte est froid. Victorina pose la main dessus. Il est froid. Oui, la pluie l'a mouillé. En ce moment, papa ouvre la porte du balcon. L'air sent la pluie et la soupe. On va regarder les toits. On reste avec un adulte. Papa, c'est l'adulte. Victorina tient le manteau de papa. Le manteau est épais et un peu humide. Pieds au sol. Derrière la protection. Victorina pose les pieds au sol. Elle sent le sol sous les chaussettes. Les chaussettes sont grises et douces. Elle reste derrière la protection. La protection est lisse sous sa main. Elle est lisse, papa. Oui. On reste derrière la protection. Victorina regarde les toits. Les tuiles sont brunes et brillantes. Le chat gris lèche une patte. Le chat, papa. Je le vois. Tes pieds au sol ? Pieds au sol. Bravo. Un pigeon passe au-dessus des tuiles. Ses ailes font un petit bruit mou. Le pigeon vole. Oui. On le regarde d'ici. Derrière la protection. Avec un adulte. Victorina serre le manteau de papa. Le vent est doux sur ses joues. Une autre goutte tombe du géranium. Elle fait tic sur le carreau. Tu as entendu la goutte ? Tic. Oui. Tu as fait du bon travail. Victorina respire l'air mouillé. Elle garde les pieds au sol. Elle reste derrière la protection. On rentre pour la soupe ? Oui, papa. Ils rentrent ensemble. Papa ferme la porte.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,12 +1324,69 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Yseult est sur le balcon avec papa. Papa, c'est l'adulte. Yseult reste derrière la protection. Ses pieds restent au sol. Le vent est doux. Yseult tient le manteau de papa.
-papa|Pieds au sol. Derrière la protection. Avec un adulte.
-narrateur|Yseult regarde les toits. Elle ne bouge pas les pieds. Papa sourit. Ils rentrent ensemble.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+          <t>narrateur|Une goutte glisse sur une feuille.
+narrateur|La feuille est d'un géranium rouge.
+narrateur|Les tuiles brillent encore.
+narrateur|La cuisine sent la soupe.
+narrateur|Un chat gris s'assoit sur le toit d'à côté.
+narrateur|Le rideau jaune bouge un peu.
+papa|Tu as vu le chat, Victorina ?
+enfant-f|Il est tout gris, papa.
+papa|Oui.
+papa|Il se tient tranquille.
+narrateur|Le carreau près de la porte est froid.
+narrateur|Victorina pose la main dessus.
+enfant-f|Il est froid.
+papa|Oui, la pluie l'a mouillé.
+narrateur|En ce moment, papa ouvre la porte du balcon.
+narrateur|L'air sent la pluie et la soupe.
+papa|On va regarder les toits.
+papa|On reste avec un adulte.
+papa|Papa, c'est l'adulte.
+narrateur|Victorina tient le manteau de papa.
+narrateur|Le manteau est épais et un peu humide.
+papa|Pieds au sol.
+papa|Derrière la protection.
+narrateur|Victorina pose les pieds au sol.
+narrateur|Elle sent le sol sous les chaussettes.
+narrateur|Les chaussettes sont grises et douces.
+narrateur|Elle reste derrière la protection.
+narrateur|La protection est lisse sous sa main.
+enfant-f|Elle est lisse, papa.
+papa|Oui.
+papa|On reste derrière la protection.
+narrateur|Victorina regarde les toits.
+narrateur|Les tuiles sont brunes et brillantes.
+narrateur|Le chat gris lèche une patte.
+enfant-f|Le chat, papa.
+papa|Je le vois.
+papa|Tes pieds au sol ?
+enfant-f|Pieds au sol.
+papa|Bravo.
+narrateur|Un pigeon passe au-dessus des tuiles.
+narrateur|Ses ailes font un petit bruit mou.
+enfant-f|Le pigeon vole.
+papa|Oui.
+papa|On le regarde d'ici.
+papa|Derrière la protection.
+papa|Avec un adulte.
+narrateur|Victorina serre le manteau de papa.
+narrateur|Le vent est doux sur ses joues.
+narrateur|Une autre goutte tombe du géranium.
+narrateur|Elle fait tic sur le carreau.
+papa|Tu as entendu la goutte ?
+enfant-f|Tic.
+papa|Oui.
+papa|Tu as fait du bon travail.
+narrateur|Victorina respire l'air mouillé.
+narrateur|Elle garde les pieds au sol.
+narrateur|Elle reste derrière la protection.
+papa|On rentre pour la soupe ?
+enfant-f|Oui, papa.
+narrateur|Ils rentrent ensemble.
+narrateur|Papa ferme la porte.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1342,7 +1411,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Yseult est sur le balcon. Que fait-elle ?</t>
+          <t>Victorina est sur le balcon. Que fait-elle ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1502,10 +1571,10 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Yseult est sur le balcon. Que fait-elle ?</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr"/>
+          <t>narrateur|Victorina est sur le balcon.
+narrateur|Que fait-elle ?</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1530,7 +1599,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Yseult a gardé les pieds au sol. Derrière la protection. Avec papa, l'adulte.</t>
+          <t>Victorina a gardé les pieds au sol. Elle est restée derrière la protection. Avec papa, l'adulte. Tu as gardé les pieds au sol ? Oui. Derrière la protection. Bravo. C'est du bon travail. Le chat est encore sur le toit. Le géranium rouge brille un peu.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1678,10 +1747,18 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Yseult a gardé les pieds au sol. Derrière la protection. Avec papa, l'adulte.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+          <t>narrateur|Victorina a gardé les pieds au sol.
+narrateur|Elle est restée derrière la protection.
+narrateur|Avec papa, l'adulte.
+papa|Tu as gardé les pieds au sol ?
+enfant-f|Oui.
+enfant-f|Derrière la protection.
+papa|Bravo.
+papa|C'est du bon travail.
+narrateur|Le chat est encore sur le toit.
+narrateur|Le géranium rouge brille un peu.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1706,7 +1783,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Papa ferme la porte. Yseult s'assoit.</t>
+          <t>La soupe fume dans les bols. Elle sent la carotte. Victorina s'assoit. Ses chaussettes grises sont un peu froides. Tu as regardé les toits avec moi ? Oui. Le chat était gris. Et tes pieds ? Pieds au sol. Derrière la protection. Avec un adulte. Bravo, Victorina. Victorina souffle sur la soupe. La vapeur chatouille son nez.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1846,10 +1923,22 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Papa ferme la porte. Yseult s'assoit.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+          <t>narrateur|La soupe fume dans les bols.
+narrateur|Elle sent la carotte.
+narrateur|Victorina s'assoit.
+narrateur|Ses chaussettes grises sont un peu froides.
+papa|Tu as regardé les toits avec moi ?
+enfant-f|Oui.
+enfant-f|Le chat était gris.
+papa|Et tes pieds ?
+enfant-f|Pieds au sol.
+papa|Derrière la protection.
+papa|Avec un adulte.
+papa|Bravo, Victorina.
+narrateur|Victorina souffle sur la soupe.
+narrateur|La vapeur chatouille son nez.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1874,7 +1963,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Le rideau jaune ne bouge plus. Les tuiles sèchent tout doucement. On a vu les toits. Oui. Pieds au sol, derrière la protection. Bravo, Victorina. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2014,10 +2103,15 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+          <t>narrateur|Le rideau jaune ne bouge plus.
+narrateur|Les tuiles sèchent tout doucement.
+enfant-f|On a vu les toits.
+papa|Oui.
+papa|Pieds au sol, derrière la protection.
+papa|Bravo, Victorina.
+narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2036,7 +2130,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2074,6 +2168,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SEC.MAI.003-07.xlsx
+++ b/stories/arbres/ATOM-SEC.MAI.003-07.xlsx
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Une goutte glisse sur une feuille. La feuille est d'un géranium rouge. Les tuiles brillent encore. La cuisine sent la soupe. Un chat gris s'assoit sur le toit d'à côté. Le rideau jaune bouge un peu. Tu as vu le chat, Victorina ? Il est tout gris, papa. Oui. Il se tient tranquille. Le carreau près de la porte est froid. Victorina pose la main dessus. Il est froid. Oui, la pluie l'a mouillé. En ce moment, papa ouvre la porte du balcon. L'air sent la pluie et la soupe. On va regarder les toits. On reste avec un adulte. Papa, c'est l'adulte. Victorina tient le manteau de papa. Le manteau est épais et un peu humide. Pieds au sol. Derrière la protection. Victorina pose les pieds au sol. Elle sent le sol sous les chaussettes. Les chaussettes sont grises et douces. Elle reste derrière la protection. La protection est lisse sous sa main. Elle est lisse, papa. Oui. On reste derrière la protection. Victorina regarde les toits. Les tuiles sont brunes et brillantes. Le chat gris lèche une patte. Le chat, papa. Je le vois. Tes pieds au sol ? Pieds au sol. Bravo. Un pigeon passe au-dessus des tuiles. Ses ailes font un petit bruit mou. Le pigeon vole. Oui. On le regarde d'ici. Derrière la protection. Avec un adulte. Victorina serre le manteau de papa. Le vent est doux sur ses joues. Une autre goutte tombe du géranium. Elle fait tic sur le carreau. Tu as entendu la goutte ? Tic. Oui. Tu as fait du bon travail. Victorina respire l'air mouillé. Elle garde les pieds au sol. Elle reste derrière la protection. On rentre pour la soupe ? Oui, papa. Ils rentrent ensemble. Papa ferme la porte.</t>
+          <t>Une goutte glisse sur une feuille. La feuille est d'un géranium rouge. Les tuiles brillent encore. La cuisine sent la soupe. Un chat gris s'assoit sur le toit d'à côté. Le rideau jaune bouge un peu. Tu as vu le chat, Victorina ? Il est tout gris, papa. Oui. Il se tient tranquille. Le carreau près de la porte est froid. Victorina pose la main dessus. Il est froid. Oui, la pluie l'a mouillé. En ce moment, papa ouvre la porte du balcon. L'air sent la pluie et la soupe. On va regarder les toits. On reste avec un adulte. Papa, c'est l'adulte. Victorina tient le manteau de papa. Le manteau est épais et un peu humide. Pieds au sol. Derrière la protection. Victorina pose les pieds au sol. Elle sent le sol sous les chaussettes. Les chaussettes sont grises et douces. Elle reste derrière la protection. La protection est lisse sous sa main. Elle est lisse, papa. Oui. On reste derrière la protection. Victorina regarde les toits. Les tuiles sont brunes et brillantes. Le chat gris lèche une patte. Le chat, papa. Je le vois. Tes pieds au sol ? Pieds au sol. Bravo. Un pigeon passe au-dessus des tuiles. Ses ailes font un petit bruit mou. Le pigeon vole. Oui. On le regarde d'ici. Derrière la protection. Avec un adulte. Victorina serre le manteau de papa. Le vent est doux sur ses joues. Une autre goutte tombe du géranium. Elle fait tic sur le carreau. Tu as entendu la goutte ? Tic. Oui. Victorina respire l'air mouillé. Elle garde les pieds au sol. Elle reste derrière la protection. On rentre pour la soupe ? Oui, papa. Ils rentrent ensemble. Papa ferme la porte.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Yseult est sur le balcon avec papa. Papa, c'est l'adulte. Yseult reste derrière la protection. Ses &lt;emphasis level="moderate"&gt;pieds&lt;/emphasis&gt; restent au sol. Le vent est doux. Yseult tient le manteau de papa. Papa dit : pieds au sol. Derrière la protection. Avec un adulte. Yseult regarde les toits. Elle ne bouge pas les pieds. Papa sourit. Ils rentrent ensemble.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Une goutte glisse sur une feuille. La feuille est d'un géranium rouge. Les tuiles brillent encore. La cuisine sent la soupe. Un chat gris s'assoit sur le toit d'à côté. Le rideau jaune bouge un peu. Tu as vu le chat, Victorina ? Il est tout gris, papa. Oui. Il se tient tranquille. Le carreau près de la porte est froid. Victorina pose la main dessus. Il est froid. Oui, la pluie l'a mouillé. En ce moment, papa ouvre la porte du balcon. L'air sent la pluie et la soupe. On va regarder les toits. On reste avec un adulte. Papa, c'est l'adulte. Victorina tient le manteau de papa. Le manteau est épais et un peu humide. Pieds au sol. Derrière la protection. Victorina pose les pieds au sol. Elle sent le sol sous les chaussettes. Les chaussettes sont grises et douces. Elle reste derrière la protection. La protection est lisse sous sa main. Elle est lisse, papa. Oui. On reste derrière la protection. Victorina regarde les toits. Les tuiles sont brunes et brillantes. Le chat gris lèche une patte. Le chat, papa. Je le vois. Tes pieds au sol ? Pieds au sol. Bravo. Un pigeon passe au-dessus des tuiles. Ses ailes font un petit bruit mou. Le pigeon vole. Oui. On le regarde d'ici. Derrière la protection. Avec un adulte. Victorina serre le manteau de papa. Le vent est doux sur ses joues. Une autre goutte tombe du géranium. Elle fait tic sur le carreau. Tu as entendu la goutte ? Tic. Oui. Victorina respire l'air mouillé. Elle garde les pieds au sol. Elle reste derrière la protection. On rentre pour la soupe ? Oui, papa. Ils rentrent ensemble. Papa ferme la porte.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1377,7 +1377,6 @@
 papa|Tu as entendu la goutte ?
 enfant-f|Tic.
 papa|Oui.
-papa|Tu as fait du bon travail.
 narrateur|Victorina respire l'air mouillé.
 narrateur|Elle garde les pieds au sol.
 narrateur|Elle reste derrière la protection.
@@ -1416,7 +1415,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;Yseult est sur le balcon. Que fait-elle ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Victorina est sur le balcon. Que fait-elle ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1599,12 +1598,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Victorina a gardé les pieds au sol. Elle est restée derrière la protection. Avec papa, l'adulte. Tu as gardé les pieds au sol ? Oui. Derrière la protection. Bravo. C'est du bon travail. Le chat est encore sur le toit. Le géranium rouge brille un peu.</t>
+          <t>Victorina a gardé les pieds au sol. Elle est restée derrière la protection. Avec papa, l'adulte. Tu as gardé les pieds au sol ? Oui. Derrière la protection. Bravo. Le chat est encore sur le toit. Le géranium rouge brille un peu.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;Yseult a gardé les &lt;emphasis level="moderate"&gt;pieds&lt;/emphasis&gt; au sol. Derrière la protection. Avec papa, l'adulte.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Victorina a gardé les pieds au sol. Elle est restée derrière la protection. Avec papa, l'adulte. Tu as gardé les pieds au sol ? Oui. Derrière la protection. Bravo. Le chat est encore sur le toit. Le géranium rouge brille un peu.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1754,7 +1753,6 @@
 enfant-f|Oui.
 enfant-f|Derrière la protection.
 papa|Bravo.
-papa|C'est du bon travail.
 narrateur|Le chat est encore sur le toit.
 narrateur|Le géranium rouge brille un peu.</t>
         </is>
@@ -1788,7 +1786,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;Papa ferme la porte. Yseult s'assoit.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>La soupe fume dans les bols. Elle sent la carotte. Victorina s'assoit. Ses chaussettes grises sont un peu froides. Tu as regardé les toits avec moi ? Oui. Le chat était gris. Et tes pieds ? Pieds au sol. Derrière la protection. Avec un adulte. Bravo, Victorina. Victorina souffle sur la soupe. La vapeur chatouille son nez.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1963,12 +1961,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Le rideau jaune ne bouge plus. Les tuiles sèchent tout doucement. On a vu les toits. Oui. Pieds au sol, derrière la protection. Bravo, Victorina. L'histoire est finie.</t>
+          <t>Le rideau jaune ne bouge plus. Les tuiles sèchent tout doucement. On a vu les toits. Oui. Pieds au sol, derrière la protection. Bravo, Victorina.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le rideau jaune ne bouge plus. Les tuiles sèchent tout doucement. On a vu les toits. Oui. Pieds au sol, derrière la protection. Bravo, Victorina.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2108,8 +2106,7 @@
 enfant-f|On a vu les toits.
 papa|Oui.
 papa|Pieds au sol, derrière la protection.
-papa|Bravo, Victorina.
-narrateur|L'histoire est finie.</t>
+papa|Bravo, Victorina.</t>
         </is>
       </c>
     </row>
@@ -2130,7 +2127,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2175,6 +2172,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SEC.MAI.003-07.xlsx
+++ b/stories/arbres/ATOM-SEC.MAI.003-07.xlsx
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>balcon</t>
+          <t>balcon après la pluie</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Yseult, papa</t>
+          <t>Victorina, papa</t>
         </is>
       </c>
     </row>
